--- a/Project Outputs for led_matrix_board/Assembly/BOM/No Template Bill of Materials-led_matrix_board.xlsx
+++ b/Project Outputs for led_matrix_board/Assembly/BOM/No Template Bill of Materials-led_matrix_board.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonathan.garnier\AppData\Local\Temp\Releases\Snapshot\1\Assembly\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9DBEC2B-AEFE-4360-ADDF-4DDA35CC3410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{687B563F-0146-446F-9CEF-DECC790130F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B6EFCD4C-FD9E-44F5-BCC9-4BE288257327}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{308283E5-A711-4ECF-A372-8C3A125D2CC4}"/>
   </bookViews>
   <sheets>
     <sheet name="No Template Bill of Materials-l" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="99">
   <si>
     <t>Comment</t>
   </si>
@@ -59,19 +59,19 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>GRM188R61E106MA73J</t>
-  </si>
-  <si>
-    <t>CAP CER 10UF 25V ±20% X5R 0603</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>0603_cap_rnd</t>
-  </si>
-  <si>
-    <t>CAP0197-9</t>
+    <t>CL32A107MPVNNNE</t>
+  </si>
+  <si>
+    <t>CAP CER 100UF 10V ±20% X5R 1210</t>
+  </si>
+  <si>
+    <t>C1, C2</t>
+  </si>
+  <si>
+    <t>CAPC3225X20N</t>
+  </si>
+  <si>
+    <t>CAP0047-3</t>
   </si>
   <si>
     <t>C0603C104K8RACTU</t>
@@ -80,7 +80,7 @@
     <t>CAP CER 100NF 10V ±10% X7R 0603</t>
   </si>
   <si>
-    <t>C2, C3, C4, C5</t>
+    <t>C3, C4, C5, C6</t>
   </si>
   <si>
     <t>0603_cap</t>
@@ -89,34 +89,34 @@
     <t>CAP0030-8</t>
   </si>
   <si>
-    <t>ESDALC6V1-1U2</t>
-  </si>
-  <si>
-    <t>TVS DIODE 3VWM ST020</t>
+    <t>XZVGR68W-3</t>
+  </si>
+  <si>
+    <t>LED GREEN 0402 SMD</t>
   </si>
   <si>
     <t>D1</t>
   </si>
   <si>
-    <t>0201_DIODE</t>
-  </si>
-  <si>
-    <t>DIO0043-4</t>
-  </si>
-  <si>
-    <t>XZVGR68W-3</t>
-  </si>
-  <si>
-    <t>LED GREEN 0402 SMD</t>
+    <t>LED_0402_GREEN</t>
+  </si>
+  <si>
+    <t>DIO0053-6</t>
+  </si>
+  <si>
+    <t>MBR120VLSFT1</t>
+  </si>
+  <si>
+    <t>Diodes, MBR120VLSFT1 Schottky 1A 20V, Vf=0.34V</t>
   </si>
   <si>
     <t>D2</t>
   </si>
   <si>
-    <t>LED_0402_GREEN</t>
-  </si>
-  <si>
-    <t>DIO0053-6</t>
+    <t>SOD-123FL</t>
+  </si>
+  <si>
+    <t>DIO0005-3</t>
   </si>
   <si>
     <t>OSTTC020162</t>
@@ -125,7 +125,7 @@
     <t>CONN TERM BLOCK 5MM 2POS</t>
   </si>
   <si>
-    <t>H1, H2</t>
+    <t>H1</t>
   </si>
   <si>
     <t>SCREW_TERM_2WAY_5MM</t>
@@ -134,19 +134,19 @@
     <t>JCK0020-1</t>
   </si>
   <si>
-    <t>SBH11-PBPC-D08-ST-BK</t>
-  </si>
-  <si>
-    <t>Conn Shrouded Header (4 Sides) HDR 16 POS 2.54mm Solder ST Top Entry Thru-Hole</t>
-  </si>
-  <si>
-    <t>H3</t>
-  </si>
-  <si>
-    <t>FP-SBH11-PBPC-D08-ST-BK-MFG</t>
-  </si>
-  <si>
-    <t>HDR0159-1</t>
+    <t>SSM-108-L-DV-K-TR</t>
+  </si>
+  <si>
+    <t>PCB Receptacle, Board-to-Board, 2.54 mm, 2 Rows, 16 Contacts, Surface Mount</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>FP-SSM-108-L-DV-K-TR-MFG</t>
+  </si>
+  <si>
+    <t>HDR0162-1</t>
   </si>
   <si>
     <t>PJ-102A</t>
@@ -176,6 +176,33 @@
     <t>PAD0008-2</t>
   </si>
   <si>
+    <t>DMP3099L-7</t>
+  </si>
+  <si>
+    <t>DMP3099L Series 30 V 65 mOhm P-Channel Enhancement Mode Mosfet - SOT-23-3</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>FP-SOT23-IPC_C</t>
+  </si>
+  <si>
+    <t>TSR0027-1</t>
+  </si>
+  <si>
+    <t>AO3400A</t>
+  </si>
+  <si>
+    <t>Trans MOSFET N-CH 30V 5.7A 3-Pin SOT-23</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>TSR0028-1</t>
+  </si>
+  <si>
     <t>MCR01MZPF3300</t>
   </si>
   <si>
@@ -191,45 +218,57 @@
     <t>RES0073-11</t>
   </si>
   <si>
+    <t>ERJ-3GEY0R00V</t>
+  </si>
+  <si>
+    <t>RES SMD 0R OHM ±1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>R2, R3, R4, R5</t>
+  </si>
+  <si>
+    <t>0603_res</t>
+  </si>
+  <si>
+    <t>RES0003-8</t>
+  </si>
+  <si>
     <t>0603WAF1002T5E</t>
   </si>
   <si>
     <t>RES SMD 10K OHM ±1% 1/10W 0603</t>
   </si>
   <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>0603_res</t>
+    <t>R6</t>
   </si>
   <si>
     <t>RES0219-8</t>
   </si>
   <si>
+    <t>0603WAF1003T5E</t>
+  </si>
+  <si>
+    <t>RES SMD 100K OHM ±1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>RES0224-8</t>
+  </si>
+  <si>
     <t>ERA-3AEB102V</t>
   </si>
   <si>
     <t>RES SMD 1K OHM ±0 .1% 1/10W 0603</t>
   </si>
   <si>
-    <t>R3</t>
+    <t>R8</t>
   </si>
   <si>
     <t>RES0105-8</t>
   </si>
   <si>
-    <t>0603WAF1003T5E</t>
-  </si>
-  <si>
-    <t>RES SMD 100K OHM ±1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>RES0224-8</t>
-  </si>
-  <si>
     <t>EVQ-PF206K</t>
   </si>
   <si>
@@ -242,13 +281,28 @@
     <t>SWH0003-1</t>
   </si>
   <si>
+    <t>MAX4866LEUT+T</t>
+  </si>
+  <si>
+    <t>Overvoltage Protection Controllers with Reverse Polarity Protection</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>MAX4866LEUT+T-Footprint-1</t>
+  </si>
+  <si>
+    <t>ICT0297-2</t>
+  </si>
+  <si>
     <t>SN74AHCT245PWR</t>
   </si>
   <si>
     <t>8mA 8 4.5V~5.5V 8mA 1 TSSOP-20 Buffer/Driver/Transceiver ROHS</t>
   </si>
   <si>
-    <t>U1, U3</t>
+    <t>U2, U4</t>
   </si>
   <si>
     <t>FP-PW0020A-IPC_A</t>
@@ -263,7 +317,7 @@
     <t>ESP32-S3-Pico Module.</t>
   </si>
   <si>
-    <t>U2</t>
+    <t>U3</t>
   </si>
   <si>
     <t>MOD0041-1</t>
@@ -275,7 +329,7 @@
     <t>Mic Omni-Directional -26dB 3.63V Rectangular Solder Pad T/R</t>
   </si>
   <si>
-    <t>U4</t>
+    <t>U5</t>
   </si>
   <si>
     <t>FP-ICS-43434-MFG</t>
@@ -677,8 +731,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{820D9FD6-0210-4428-AC9A-BBDE28BE408C}">
-  <dimension ref="A1:F17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3CF7A74-2928-4766-88CD-C826179A4E4A}">
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="6" width="18.81640625" customWidth="1"/>
@@ -721,7 +775,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -801,7 +855,7 @@
         <v>30</v>
       </c>
       <c r="F6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -895,10 +949,10 @@
         <v>52</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="F11" s="1">
         <v>1</v>
@@ -906,16 +960,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>58</v>
@@ -935,30 +989,30 @@
         <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F13" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
@@ -966,22 +1020,22 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>71</v>
       </c>
       <c r="F15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -995,7 +1049,7 @@
         <v>74</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>75</v>
@@ -1015,12 +1069,92 @@
         <v>78</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="1">
+      <c r="B18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21" s="1">
         <v>1</v>
       </c>
     </row>
